--- a/artfynd/A 9071-2026 artfynd.xlsx
+++ b/artfynd/A 9071-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,8512 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131824941</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>497158</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6665848</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131815946</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>497370</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6665890</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131815750</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>497401</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6665928</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131826065</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>497022</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6666032</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131823377</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497013</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6665916</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131819996</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>496731</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6665630</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131820483</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>496755</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6665498</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131823127</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>497008</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6665856</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131812867</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>497046</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6666114</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt, 200+.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131817895</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93120</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>497114</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6665644</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131813222</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97278</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>497070</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6666043</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131812941</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>497063</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6666103</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131817878</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93120</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>497115</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6665636</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131813411</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497031</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6666011</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131817592</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>497156</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6665625</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131825446</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>497225</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6665902</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Skalad klen gran.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131813949</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>497132</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6665999</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131820198</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496724</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6665629</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131822287</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496800</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6665757</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131820090</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>496724</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6665629</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131822481</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>496867</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6665758</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131822631</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>496916</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6665758</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131819438</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>496909</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6665623</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131814639</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>497222</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6665985</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131819620</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>496839</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6665620</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131822891</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>496991</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6665792</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131823937</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>496961</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6665968</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131820211</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>496715</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6665621</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131813803</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>497075</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6665986</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131822613</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>496886</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6665791</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131812738</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>497044</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6666126</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131821919</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>496673</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6665715</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131820260</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>496750</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6665593</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131813256</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>497050</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6666028</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131821816</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>496659</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6665733</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131820988</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91853</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>496679</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6665484</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131826218</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>496988</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6666049</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131820461</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>496750</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6665519</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131817253</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97278</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>53</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>497240</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6665672</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt på låga, naturskogskaraktär. Opåverkat.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131813324</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>497037</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6666041</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Möjlig början till bobygge. Tall.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131820286</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>496750</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6665593</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131816700</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>497217</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6665802</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131824551</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>497094</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6665962</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131820420</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>496739</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6665550</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131820034</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>496723</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6665623</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131815569</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>497435</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6665962</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131822460</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>496866</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6665758</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131823667</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>496999</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6665942</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131815592</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>497422</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6665955</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131814230</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>497196</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6665988</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131816514</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>497264</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6665784</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131816009</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>497376</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6665876</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131814218</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>497196</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6665980</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131820897</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>496659</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6665450</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131819420</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>496910</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6665624</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131819462</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>496908</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6665623</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Gran, naturskogskaraktär.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131826203</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>496987</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6666050</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131825046</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>497155</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6665825</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131812974</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>497066</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6666099</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131814895</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>497309</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6666024</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131824196</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>497013</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6665983</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Barkfläk, flera barkborre skadade granar. Hagelsvärm.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131813681</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>497049</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6665989</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131820394</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>496729</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6665578</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131823511</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91846</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>497000</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6665921</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131817993</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>497109</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6665663</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska och äldre.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131821003</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>496677</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6665493</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131822008</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>496703</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6665712</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>131820601</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>496774</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6665442</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gammal tall, inte jätte gammalt hål.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131813190</v>
+      </c>
+      <c r="B71" t="n">
+        <v>97278</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>53</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>497078</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6666034</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131820687</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>496727</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6665448</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131814741</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>497276</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6666012</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131825840</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Saxberget, Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>497171</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6665994</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131824427</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>497048</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6665991</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Inte jättegamla. Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131822045</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>496716</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6665704</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131823795</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>496953</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6665935</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Barkfläk, mycket små flagor under träd.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131822816</v>
+      </c>
+      <c r="B78" t="n">
+        <v>93120</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>496977</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6665784</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Intill kolbotten</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9071-2026 artfynd.xlsx
+++ b/artfynd/A 9071-2026 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131824941</v>
+        <v>131819996</v>
       </c>
       <c r="B3" t="n">
         <v>79264</v>
@@ -808,14 +808,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497158</v>
+        <v>496731</v>
       </c>
       <c r="R3" t="n">
-        <v>6665848</v>
+        <v>6665630</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131815946</v>
+        <v>131815750</v>
       </c>
       <c r="B4" t="n">
-        <v>91795</v>
+        <v>91832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497370</v>
+        <v>497401</v>
       </c>
       <c r="R4" t="n">
-        <v>6665890</v>
+        <v>6665928</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -954,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131815750</v>
+        <v>131824941</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497401</v>
+        <v>497158</v>
       </c>
       <c r="R5" t="n">
-        <v>6665928</v>
+        <v>6665848</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1061,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131823377</v>
+        <v>131820483</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,19 +1221,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1236,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497013</v>
+        <v>496755</v>
       </c>
       <c r="R7" t="n">
-        <v>6665916</v>
+        <v>6665498</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1271,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1281,7 +1290,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131819996</v>
+        <v>131823377</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,23 +1333,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1343,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496731</v>
+        <v>497013</v>
       </c>
       <c r="R8" t="n">
-        <v>6665630</v>
+        <v>6665916</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1378,7 +1388,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1388,12 +1398,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,45 +1425,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131820483</v>
+        <v>131815946</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496755</v>
+        <v>497370</v>
       </c>
       <c r="R9" t="n">
-        <v>6665498</v>
+        <v>6665890</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1490,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,12 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1891,45 +1891,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131813222</v>
+        <v>131817878</v>
       </c>
       <c r="B13" t="n">
-        <v>97278</v>
+        <v>93120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497070</v>
+        <v>497115</v>
       </c>
       <c r="R13" t="n">
-        <v>6666043</v>
+        <v>6665636</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1961,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,7 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,50 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131812941</v>
+        <v>131813222</v>
       </c>
       <c r="B14" t="n">
-        <v>99038</v>
+        <v>97278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497063</v>
+        <v>497070</v>
       </c>
       <c r="R14" t="n">
-        <v>6666103</v>
+        <v>6666043</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,54 +2114,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131817878</v>
+        <v>131812941</v>
       </c>
       <c r="B15" t="n">
-        <v>93120</v>
+        <v>99038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497115</v>
+        <v>497063</v>
       </c>
       <c r="R15" t="n">
-        <v>6665636</v>
+        <v>6666103</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,45 +2226,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131813411</v>
+        <v>131825446</v>
       </c>
       <c r="B16" t="n">
-        <v>91795</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497031</v>
+        <v>497225</v>
       </c>
       <c r="R16" t="n">
-        <v>6666011</v>
+        <v>6665902</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2296,7 +2301,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2306,7 +2311,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Skalad klen gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2333,50 +2343,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131817592</v>
+        <v>131813411</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>91795</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497156</v>
+        <v>497031</v>
       </c>
       <c r="R17" t="n">
-        <v>6665625</v>
+        <v>6666011</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131825446</v>
+        <v>131817592</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,16 +2461,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2476,7 +2481,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2485,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497225</v>
+        <v>497156</v>
       </c>
       <c r="R18" t="n">
-        <v>6665902</v>
+        <v>6665625</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2520,7 +2525,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,12 +2535,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Skalad klen gran.</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131822287</v>
+        <v>131820090</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496800</v>
+        <v>496724</v>
       </c>
       <c r="R21" t="n">
-        <v>6665757</v>
+        <v>6665629</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,12 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2893,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131820090</v>
+        <v>131822631</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,34 +2899,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496724</v>
+        <v>496916</v>
       </c>
       <c r="R22" t="n">
-        <v>6665629</v>
+        <v>6665758</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2973,7 +2973,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,10 +3112,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131822631</v>
+        <v>131822287</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,39 +3123,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496916</v>
+        <v>496800</v>
       </c>
       <c r="R24" t="n">
-        <v>6665758</v>
+        <v>6665757</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3336,50 +3336,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131814639</v>
+        <v>131822891</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>91795</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497222</v>
+        <v>496991</v>
       </c>
       <c r="R26" t="n">
-        <v>6665985</v>
+        <v>6665792</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3411,7 +3406,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3421,12 +3416,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3565,32 +3555,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131822891</v>
+        <v>131823937</v>
       </c>
       <c r="B28" t="n">
-        <v>91795</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3600,10 +3590,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496991</v>
+        <v>496961</v>
       </c>
       <c r="R28" t="n">
-        <v>6665792</v>
+        <v>6665968</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3635,7 +3625,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3645,7 +3635,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3672,10 +3662,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131823937</v>
+        <v>131814639</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,34 +3673,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496961</v>
+        <v>497222</v>
       </c>
       <c r="R29" t="n">
-        <v>6665968</v>
+        <v>6665985</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3742,7 +3737,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3752,7 +3747,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3779,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131820211</v>
+        <v>131813803</v>
       </c>
       <c r="B30" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3790,34 +3790,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496715</v>
+        <v>497075</v>
       </c>
       <c r="R30" t="n">
-        <v>6665621</v>
+        <v>6665986</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3849,7 +3854,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3859,12 +3864,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3891,10 +3891,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131813803</v>
+        <v>131820211</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3902,39 +3902,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497075</v>
+        <v>496715</v>
       </c>
       <c r="R31" t="n">
-        <v>6665986</v>
+        <v>6665621</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3966,7 +3961,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3976,7 +3971,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4003,45 +4003,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131822613</v>
+        <v>131812738</v>
       </c>
       <c r="B32" t="n">
-        <v>79264</v>
+        <v>99038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496886</v>
+        <v>497044</v>
       </c>
       <c r="R32" t="n">
-        <v>6665791</v>
+        <v>6666126</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4073,7 +4087,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4083,7 +4097,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4110,47 +4124,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131812738</v>
+        <v>131820988</v>
       </c>
       <c r="B33" t="n">
-        <v>99038</v>
+        <v>91853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4159,10 +4168,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497044</v>
+        <v>496679</v>
       </c>
       <c r="R33" t="n">
-        <v>6666126</v>
+        <v>6665484</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4194,7 +4203,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4204,7 +4213,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4231,7 +4245,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131821919</v>
+        <v>131821816</v>
       </c>
       <c r="B34" t="n">
         <v>79264</v>
@@ -4266,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496673</v>
+        <v>496659</v>
       </c>
       <c r="R34" t="n">
-        <v>6665715</v>
+        <v>6665733</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4301,7 +4315,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4311,7 +4325,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4343,10 +4357,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131820260</v>
+        <v>131821919</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,39 +4368,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496750</v>
+        <v>496673</v>
       </c>
       <c r="R35" t="n">
-        <v>6665593</v>
+        <v>6665715</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4418,7 +4427,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4428,7 +4437,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4455,32 +4469,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131813256</v>
+        <v>131826218</v>
       </c>
       <c r="B36" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4490,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497050</v>
+        <v>496988</v>
       </c>
       <c r="R36" t="n">
-        <v>6666028</v>
+        <v>6666049</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4525,7 +4539,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4535,12 +4549,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4567,7 +4576,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131821816</v>
+        <v>131820461</v>
       </c>
       <c r="B37" t="n">
         <v>79264</v>
@@ -4602,10 +4611,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496659</v>
+        <v>496750</v>
       </c>
       <c r="R37" t="n">
-        <v>6665733</v>
+        <v>6665519</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4637,7 +4646,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4647,7 +4656,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4679,10 +4688,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131820988</v>
+        <v>131820260</v>
       </c>
       <c r="B38" t="n">
-        <v>91853</v>
+        <v>57899</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4690,31 +4699,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4723,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496679</v>
+        <v>496750</v>
       </c>
       <c r="R38" t="n">
-        <v>6665484</v>
+        <v>6665593</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4758,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4768,12 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,32 +4800,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131826218</v>
+        <v>131822613</v>
       </c>
       <c r="B39" t="n">
-        <v>91795</v>
+        <v>79264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496988</v>
+        <v>496886</v>
       </c>
       <c r="R39" t="n">
-        <v>6666049</v>
+        <v>6665791</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4907,7 +4907,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131820461</v>
+        <v>131813256</v>
       </c>
       <c r="B40" t="n">
         <v>79264</v>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496750</v>
+        <v>497050</v>
       </c>
       <c r="R40" t="n">
-        <v>6665519</v>
+        <v>6666028</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131817253</v>
+        <v>131820286</v>
       </c>
       <c r="B41" t="n">
-        <v>97278</v>
+        <v>79264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5030,34 +5030,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497240</v>
+        <v>496750</v>
       </c>
       <c r="R41" t="n">
-        <v>6665672</v>
+        <v>6665593</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt på låga, naturskogskaraktär. Opåverkat.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5131,10 +5131,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131813324</v>
+        <v>131817253</v>
       </c>
       <c r="B42" t="n">
-        <v>57899</v>
+        <v>97278</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5142,34 +5142,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497037</v>
+        <v>497240</v>
       </c>
       <c r="R42" t="n">
-        <v>6666041</v>
+        <v>6665672</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Möjlig början till bobygge. Tall.</t>
+          <t>Rikligt på låga, naturskogskaraktär. Opåverkat.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5243,10 +5243,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131820286</v>
+        <v>131813324</v>
       </c>
       <c r="B43" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5254,21 +5254,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496750</v>
+        <v>497037</v>
       </c>
       <c r="R43" t="n">
-        <v>6665593</v>
+        <v>6666041</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Möjlig början till bobygge. Tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5355,38 +5355,47 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131816700</v>
+        <v>131824551</v>
       </c>
       <c r="B44" t="n">
-        <v>57902</v>
+        <v>99038</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5395,10 +5404,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497217</v>
+        <v>497094</v>
       </c>
       <c r="R44" t="n">
-        <v>6665802</v>
+        <v>6665962</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5430,7 +5439,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5440,12 +5449,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5472,59 +5476,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131824551</v>
+        <v>131820420</v>
       </c>
       <c r="B45" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497094</v>
+        <v>496739</v>
       </c>
       <c r="R45" t="n">
-        <v>6665962</v>
+        <v>6665550</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5556,7 +5546,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5566,7 +5556,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5593,10 +5588,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131820420</v>
+        <v>131816700</v>
       </c>
       <c r="B46" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5604,34 +5599,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496739</v>
+        <v>497217</v>
       </c>
       <c r="R46" t="n">
-        <v>6665550</v>
+        <v>6665802</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5817,10 +5817,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131815569</v>
+        <v>131822460</v>
       </c>
       <c r="B48" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5828,39 +5828,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497435</v>
+        <v>496866</v>
       </c>
       <c r="R48" t="n">
-        <v>6665962</v>
+        <v>6665758</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5892,7 +5887,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5902,7 +5897,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5929,10 +5924,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131822460</v>
+        <v>131815569</v>
       </c>
       <c r="B49" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5940,34 +5935,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496866</v>
+        <v>497435</v>
       </c>
       <c r="R49" t="n">
-        <v>6665758</v>
+        <v>6665962</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6143,7 +6143,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131815592</v>
+        <v>131814230</v>
       </c>
       <c r="B51" t="n">
         <v>91795</v>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497422</v>
+        <v>497196</v>
       </c>
       <c r="R51" t="n">
-        <v>6665955</v>
+        <v>6665988</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6250,7 +6250,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131814230</v>
+        <v>131815592</v>
       </c>
       <c r="B52" t="n">
         <v>91795</v>
@@ -6285,10 +6285,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497196</v>
+        <v>497422</v>
       </c>
       <c r="R52" t="n">
-        <v>6665988</v>
+        <v>6665955</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6357,50 +6357,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131816514</v>
+        <v>131820897</v>
       </c>
       <c r="B53" t="n">
-        <v>57902</v>
+        <v>5178</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497264</v>
+        <v>496659</v>
       </c>
       <c r="R53" t="n">
-        <v>6665784</v>
+        <v>6665450</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6442,12 +6442,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6474,7 +6469,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131816009</v>
+        <v>131819420</v>
       </c>
       <c r="B54" t="n">
         <v>57899</v>
@@ -6505,19 +6500,19 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497376</v>
+        <v>496910</v>
       </c>
       <c r="R54" t="n">
-        <v>6665876</v>
+        <v>6665624</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6549,7 +6544,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6559,7 +6554,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6698,50 +6693,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131820897</v>
+        <v>131816514</v>
       </c>
       <c r="B56" t="n">
-        <v>5178</v>
+        <v>57902</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496659</v>
+        <v>497264</v>
       </c>
       <c r="R56" t="n">
-        <v>6665450</v>
+        <v>6665784</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6773,7 +6768,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6783,7 +6778,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6810,7 +6810,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131819420</v>
+        <v>131816009</v>
       </c>
       <c r="B57" t="n">
         <v>57899</v>
@@ -6841,19 +6841,19 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496910</v>
+        <v>497376</v>
       </c>
       <c r="R57" t="n">
-        <v>6665624</v>
+        <v>6665876</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6922,7 +6922,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131819462</v>
+        <v>131825046</v>
       </c>
       <c r="B58" t="n">
         <v>79264</v>
@@ -6953,14 +6953,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496908</v>
+        <v>497155</v>
       </c>
       <c r="R58" t="n">
-        <v>6665623</v>
+        <v>6665825</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7002,12 +7002,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Gran, naturskogskaraktär.</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7146,7 +7141,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131825046</v>
+        <v>131819462</v>
       </c>
       <c r="B60" t="n">
         <v>79264</v>
@@ -7177,14 +7172,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497155</v>
+        <v>496908</v>
       </c>
       <c r="R60" t="n">
-        <v>6665825</v>
+        <v>6665623</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7216,7 +7211,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7226,7 +7221,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Gran, naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7930,10 +7930,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131817993</v>
+        <v>131822008</v>
       </c>
       <c r="B67" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7941,39 +7941,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497109</v>
+        <v>496703</v>
       </c>
       <c r="R67" t="n">
-        <v>6665663</v>
+        <v>6665712</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8005,7 +8000,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8015,12 +8010,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska och äldre.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8047,10 +8042,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131821003</v>
+        <v>131820687</v>
       </c>
       <c r="B68" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8058,34 +8053,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496677</v>
+        <v>496727</v>
       </c>
       <c r="R68" t="n">
-        <v>6665493</v>
+        <v>6665448</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8127,12 +8127,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8159,10 +8154,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131822008</v>
+        <v>131817993</v>
       </c>
       <c r="B69" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8170,34 +8165,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496703</v>
+        <v>497109</v>
       </c>
       <c r="R69" t="n">
-        <v>6665712</v>
+        <v>6665663</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Färska och äldre.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8271,10 +8271,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131820601</v>
+        <v>131821003</v>
       </c>
       <c r="B70" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8282,39 +8282,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496774</v>
+        <v>496677</v>
       </c>
       <c r="R70" t="n">
-        <v>6665442</v>
+        <v>6665493</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8346,7 +8341,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8356,12 +8351,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Gammal tall, inte jätte gammalt hål.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8388,10 +8383,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131813190</v>
+        <v>131820601</v>
       </c>
       <c r="B71" t="n">
-        <v>97278</v>
+        <v>57899</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8399,34 +8394,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497078</v>
+        <v>496774</v>
       </c>
       <c r="R71" t="n">
-        <v>6666034</v>
+        <v>6665442</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8468,7 +8468,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Gammal tall, inte jätte gammalt hål.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8495,10 +8500,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131820687</v>
+        <v>131813190</v>
       </c>
       <c r="B72" t="n">
-        <v>57899</v>
+        <v>97278</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8506,39 +8511,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496727</v>
+        <v>497078</v>
       </c>
       <c r="R72" t="n">
-        <v>6665448</v>
+        <v>6666034</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8821,7 +8821,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131824427</v>
+        <v>131823795</v>
       </c>
       <c r="B75" t="n">
         <v>57902</v>
@@ -8850,21 +8850,16 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497048</v>
+        <v>496953</v>
       </c>
       <c r="R75" t="n">
-        <v>6665991</v>
+        <v>6665935</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8896,7 +8891,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8906,12 +8901,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Inte jättegamla. Rikligt.</t>
+          <t>Barkfläk, mycket små flagor under träd.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9050,45 +9045,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131823795</v>
+        <v>131822816</v>
       </c>
       <c r="B77" t="n">
-        <v>57902</v>
+        <v>93120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496953</v>
+        <v>496977</v>
       </c>
       <c r="R77" t="n">
-        <v>6665935</v>
+        <v>6665784</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9120,7 +9124,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9130,12 +9134,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Barkfläk, mycket små flagor under träd.</t>
+          <t>Intill kolbotten</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9162,42 +9166,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131822816</v>
+        <v>131824427</v>
       </c>
       <c r="B78" t="n">
-        <v>93120</v>
+        <v>57902</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9206,10 +9206,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496977</v>
+        <v>497048</v>
       </c>
       <c r="R78" t="n">
-        <v>6665784</v>
+        <v>6665991</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Intill kolbotten</t>
+          <t>Inte jättegamla. Rikligt.</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 9071-2026 artfynd.xlsx
+++ b/artfynd/A 9071-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131815750</v>
+        <v>131824941</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497401</v>
+        <v>497158</v>
       </c>
       <c r="R4" t="n">
-        <v>6665928</v>
+        <v>6665848</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131824941</v>
+        <v>131826065</v>
       </c>
       <c r="B5" t="n">
         <v>79264</v>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497158</v>
+        <v>497022</v>
       </c>
       <c r="R5" t="n">
-        <v>6665848</v>
+        <v>6666032</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131826065</v>
+        <v>131820483</v>
       </c>
       <c r="B6" t="n">
         <v>79264</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497022</v>
+        <v>496755</v>
       </c>
       <c r="R6" t="n">
-        <v>6666032</v>
+        <v>6665498</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131820483</v>
+        <v>131823377</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,23 +1226,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1245,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496755</v>
+        <v>497013</v>
       </c>
       <c r="R7" t="n">
-        <v>6665498</v>
+        <v>6665916</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1281,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,12 +1291,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,41 +1318,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131823377</v>
+        <v>131815946</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497013</v>
+        <v>497370</v>
       </c>
       <c r="R8" t="n">
-        <v>6665916</v>
+        <v>6665890</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131815946</v>
+        <v>131815750</v>
       </c>
       <c r="B9" t="n">
-        <v>91795</v>
+        <v>91832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497370</v>
+        <v>497401</v>
       </c>
       <c r="R9" t="n">
-        <v>6665890</v>
+        <v>6665928</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2226,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131825446</v>
+        <v>131817592</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,16 +2237,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2257,7 +2257,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497225</v>
+        <v>497156</v>
       </c>
       <c r="R16" t="n">
-        <v>6665902</v>
+        <v>6665625</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2311,12 +2311,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Skalad klen gran.</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,45 +2338,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131813411</v>
+        <v>131813949</v>
       </c>
       <c r="B17" t="n">
-        <v>91795</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497031</v>
+        <v>497132</v>
       </c>
       <c r="R17" t="n">
-        <v>6666011</v>
+        <v>6665999</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,50 +2450,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131817592</v>
+        <v>131813411</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>91795</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497156</v>
+        <v>497031</v>
       </c>
       <c r="R18" t="n">
-        <v>6665625</v>
+        <v>6666011</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2525,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2535,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131813949</v>
+        <v>131825446</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,16 +2568,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2593,7 +2588,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2602,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497132</v>
+        <v>497225</v>
       </c>
       <c r="R19" t="n">
-        <v>6665999</v>
+        <v>6665902</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2637,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2647,7 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Skalad klen gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131820198</v>
+        <v>131820090</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131820090</v>
+        <v>131820198</v>
       </c>
       <c r="B21" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131822631</v>
+        <v>131822481</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,36 +2899,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496916</v>
+        <v>496867</v>
       </c>
       <c r="R22" t="n">
         <v>6665758</v>
@@ -2963,7 +2958,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2973,12 +2968,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3005,7 +2995,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131822481</v>
+        <v>131822287</v>
       </c>
       <c r="B23" t="n">
         <v>79264</v>
@@ -3040,10 +3030,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496867</v>
+        <v>496800</v>
       </c>
       <c r="R23" t="n">
-        <v>6665758</v>
+        <v>6665757</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3075,7 +3065,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3085,7 +3075,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3112,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131822287</v>
+        <v>131822631</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3123,34 +3118,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496800</v>
+        <v>496916</v>
       </c>
       <c r="R24" t="n">
-        <v>6665757</v>
+        <v>6665758</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3224,32 +3224,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131819438</v>
+        <v>131822891</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496909</v>
+        <v>496991</v>
       </c>
       <c r="R25" t="n">
-        <v>6665623</v>
+        <v>6665792</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3304,12 +3304,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3336,45 +3331,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131822891</v>
+        <v>131814639</v>
       </c>
       <c r="B26" t="n">
-        <v>91795</v>
+        <v>57902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496991</v>
+        <v>497222</v>
       </c>
       <c r="R26" t="n">
-        <v>6665792</v>
+        <v>6665985</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3416,7 +3416,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,7 +3448,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131819620</v>
+        <v>131819438</v>
       </c>
       <c r="B27" t="n">
         <v>79264</v>
@@ -3478,10 +3483,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496839</v>
+        <v>496909</v>
       </c>
       <c r="R27" t="n">
-        <v>6665620</v>
+        <v>6665623</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3513,7 +3518,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3523,12 +3528,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3555,7 +3560,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131823937</v>
+        <v>131819620</v>
       </c>
       <c r="B28" t="n">
         <v>79264</v>
@@ -3590,10 +3595,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496961</v>
+        <v>496839</v>
       </c>
       <c r="R28" t="n">
-        <v>6665968</v>
+        <v>6665620</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3625,7 +3630,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3635,7 +3640,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3662,10 +3672,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131814639</v>
+        <v>131823937</v>
       </c>
       <c r="B29" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3673,39 +3683,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497222</v>
+        <v>496961</v>
       </c>
       <c r="R29" t="n">
-        <v>6665985</v>
+        <v>6665968</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3737,7 +3742,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3747,12 +3752,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3779,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131813803</v>
+        <v>131820211</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3790,39 +3790,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497075</v>
+        <v>496715</v>
       </c>
       <c r="R30" t="n">
-        <v>6665986</v>
+        <v>6665621</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3854,7 +3849,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3864,7 +3859,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3891,7 +3891,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131820211</v>
+        <v>131821816</v>
       </c>
       <c r="B31" t="n">
         <v>79264</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496715</v>
+        <v>496659</v>
       </c>
       <c r="R31" t="n">
-        <v>6665621</v>
+        <v>6665733</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4003,59 +4003,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131812738</v>
+        <v>131821919</v>
       </c>
       <c r="B32" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497044</v>
+        <v>496673</v>
       </c>
       <c r="R32" t="n">
-        <v>6666126</v>
+        <v>6665715</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4087,7 +4073,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4097,7 +4083,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4124,10 +4115,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131820988</v>
+        <v>131820461</v>
       </c>
       <c r="B33" t="n">
-        <v>91853</v>
+        <v>79264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,43 +4126,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496679</v>
+        <v>496750</v>
       </c>
       <c r="R33" t="n">
-        <v>6665484</v>
+        <v>6665519</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4203,7 +4185,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4213,12 +4195,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4245,7 +4227,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131821816</v>
+        <v>131822613</v>
       </c>
       <c r="B34" t="n">
         <v>79264</v>
@@ -4280,10 +4262,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496659</v>
+        <v>496886</v>
       </c>
       <c r="R34" t="n">
-        <v>6665733</v>
+        <v>6665791</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4315,7 +4297,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4325,12 +4307,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4357,7 +4334,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131821919</v>
+        <v>131813256</v>
       </c>
       <c r="B35" t="n">
         <v>79264</v>
@@ -4392,10 +4369,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496673</v>
+        <v>497050</v>
       </c>
       <c r="R35" t="n">
-        <v>6665715</v>
+        <v>6666028</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4427,7 +4404,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4437,7 +4414,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4469,45 +4446,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131826218</v>
+        <v>131813803</v>
       </c>
       <c r="B36" t="n">
-        <v>91795</v>
+        <v>57899</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496988</v>
+        <v>497075</v>
       </c>
       <c r="R36" t="n">
-        <v>6666049</v>
+        <v>6665986</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4539,7 +4521,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4549,7 +4531,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4576,10 +4558,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131820461</v>
+        <v>131820260</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4587,24 +4569,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
@@ -4614,7 +4601,7 @@
         <v>496750</v>
       </c>
       <c r="R37" t="n">
-        <v>6665519</v>
+        <v>6665593</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4646,7 +4633,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4656,12 +4643,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4688,38 +4670,47 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131820260</v>
+        <v>131812738</v>
       </c>
       <c r="B38" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4728,10 +4719,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496750</v>
+        <v>497044</v>
       </c>
       <c r="R38" t="n">
-        <v>6665593</v>
+        <v>6666126</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4763,7 +4754,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4773,7 +4764,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,10 +4791,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131822613</v>
+        <v>131820988</v>
       </c>
       <c r="B39" t="n">
-        <v>79264</v>
+        <v>91853</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4811,34 +4802,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496886</v>
+        <v>496679</v>
       </c>
       <c r="R39" t="n">
-        <v>6665791</v>
+        <v>6665484</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4880,7 +4880,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4907,32 +4912,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131813256</v>
+        <v>131826218</v>
       </c>
       <c r="B40" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4942,10 +4947,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497050</v>
+        <v>496988</v>
       </c>
       <c r="R40" t="n">
-        <v>6666028</v>
+        <v>6666049</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4977,7 +4982,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4987,12 +4992,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131820286</v>
+        <v>131817253</v>
       </c>
       <c r="B41" t="n">
-        <v>79264</v>
+        <v>97278</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5030,34 +5030,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496750</v>
+        <v>497240</v>
       </c>
       <c r="R41" t="n">
-        <v>6665593</v>
+        <v>6665672</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Rikligt på låga, naturskogskaraktär. Opåverkat.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5131,10 +5131,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131817253</v>
+        <v>131820286</v>
       </c>
       <c r="B42" t="n">
-        <v>97278</v>
+        <v>79264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5142,34 +5142,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497240</v>
+        <v>496750</v>
       </c>
       <c r="R42" t="n">
-        <v>6665672</v>
+        <v>6665593</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt på låga, naturskogskaraktär. Opåverkat.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5355,59 +5355,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131824551</v>
+        <v>131820420</v>
       </c>
       <c r="B44" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497094</v>
+        <v>496739</v>
       </c>
       <c r="R44" t="n">
-        <v>6665962</v>
+        <v>6665550</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5439,7 +5425,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5449,7 +5435,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5476,10 +5467,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131820420</v>
+        <v>131816700</v>
       </c>
       <c r="B45" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5487,34 +5478,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496739</v>
+        <v>497217</v>
       </c>
       <c r="R45" t="n">
-        <v>6665550</v>
+        <v>6665802</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5546,7 +5542,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5556,12 +5552,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5588,38 +5584,47 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131816700</v>
+        <v>131824551</v>
       </c>
       <c r="B46" t="n">
-        <v>57902</v>
+        <v>99038</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5628,10 +5633,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497217</v>
+        <v>497094</v>
       </c>
       <c r="R46" t="n">
-        <v>6665802</v>
+        <v>6665962</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5663,7 +5668,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5673,12 +5678,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6357,50 +6357,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131820897</v>
+        <v>131814218</v>
       </c>
       <c r="B53" t="n">
-        <v>5178</v>
+        <v>57899</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496659</v>
+        <v>497196</v>
       </c>
       <c r="R53" t="n">
-        <v>6665450</v>
+        <v>6665980</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6469,7 +6469,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131819420</v>
+        <v>131816009</v>
       </c>
       <c r="B54" t="n">
         <v>57899</v>
@@ -6500,19 +6500,19 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496910</v>
+        <v>497376</v>
       </c>
       <c r="R54" t="n">
-        <v>6665624</v>
+        <v>6665876</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6581,7 +6581,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131814218</v>
+        <v>131819420</v>
       </c>
       <c r="B55" t="n">
         <v>57899</v>
@@ -6617,14 +6617,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497196</v>
+        <v>496910</v>
       </c>
       <c r="R55" t="n">
-        <v>6665980</v>
+        <v>6665624</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6693,50 +6693,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131816514</v>
+        <v>131820897</v>
       </c>
       <c r="B56" t="n">
-        <v>57902</v>
+        <v>5178</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497264</v>
+        <v>496659</v>
       </c>
       <c r="R56" t="n">
-        <v>6665784</v>
+        <v>6665450</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6778,12 +6778,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6810,10 +6805,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131816009</v>
+        <v>131816514</v>
       </c>
       <c r="B57" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6821,16 +6816,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6850,10 +6845,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497376</v>
+        <v>497264</v>
       </c>
       <c r="R57" t="n">
-        <v>6665876</v>
+        <v>6665784</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6885,7 +6880,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6895,7 +6890,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7029,50 +7029,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131826203</v>
+        <v>131819462</v>
       </c>
       <c r="B59" t="n">
-        <v>5178</v>
+        <v>79264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496987</v>
+        <v>496908</v>
       </c>
       <c r="R59" t="n">
-        <v>6666050</v>
+        <v>6665623</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7104,7 +7099,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7114,7 +7109,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Gran, naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7141,45 +7141,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131819462</v>
+        <v>131826203</v>
       </c>
       <c r="B60" t="n">
-        <v>79264</v>
+        <v>5178</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496908</v>
+        <v>496987</v>
       </c>
       <c r="R60" t="n">
-        <v>6665623</v>
+        <v>6666050</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7211,7 +7216,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7221,12 +7226,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Gran, naturskogskaraktär.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7477,10 +7477,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131824196</v>
+        <v>131823511</v>
       </c>
       <c r="B63" t="n">
-        <v>57902</v>
+        <v>91846</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7488,39 +7488,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497013</v>
+        <v>497000</v>
       </c>
       <c r="R63" t="n">
-        <v>6665983</v>
+        <v>6665921</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7552,7 +7547,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7562,12 +7557,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Barkfläk, flera barkborre skadade granar. Hagelsvärm.</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7594,10 +7584,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131813681</v>
+        <v>131820394</v>
       </c>
       <c r="B64" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7605,39 +7595,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497049</v>
+        <v>496729</v>
       </c>
       <c r="R64" t="n">
-        <v>6665989</v>
+        <v>6665578</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7669,7 +7654,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7679,12 +7664,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7711,10 +7696,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131820394</v>
+        <v>131813681</v>
       </c>
       <c r="B65" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7722,34 +7707,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496729</v>
+        <v>497049</v>
       </c>
       <c r="R65" t="n">
-        <v>6665578</v>
+        <v>6665989</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7781,7 +7771,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7791,12 +7781,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7823,10 +7813,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131823511</v>
+        <v>131824196</v>
       </c>
       <c r="B66" t="n">
-        <v>91846</v>
+        <v>57902</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7834,34 +7824,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497000</v>
+        <v>497013</v>
       </c>
       <c r="R66" t="n">
-        <v>6665921</v>
+        <v>6665983</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7893,7 +7888,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7903,7 +7898,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Barkfläk, flera barkborre skadade granar. Hagelsvärm.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8042,10 +8042,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131820687</v>
+        <v>131821003</v>
       </c>
       <c r="B68" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8053,39 +8053,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496727</v>
+        <v>496677</v>
       </c>
       <c r="R68" t="n">
-        <v>6665448</v>
+        <v>6665493</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8117,7 +8112,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8127,7 +8122,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8154,7 +8154,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131817993</v>
+        <v>131820687</v>
       </c>
       <c r="B69" t="n">
         <v>57899</v>
@@ -8190,14 +8190,14 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497109</v>
+        <v>496727</v>
       </c>
       <c r="R69" t="n">
-        <v>6665663</v>
+        <v>6665448</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8239,12 +8239,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska och äldre.</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8271,10 +8266,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131821003</v>
+        <v>131817993</v>
       </c>
       <c r="B70" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8282,34 +8277,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496677</v>
+        <v>497109</v>
       </c>
       <c r="R70" t="n">
-        <v>6665493</v>
+        <v>6665663</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Färska och äldre.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8933,10 +8933,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131822045</v>
+        <v>131824427</v>
       </c>
       <c r="B76" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8944,34 +8944,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496716</v>
+        <v>497048</v>
       </c>
       <c r="R76" t="n">
-        <v>6665704</v>
+        <v>6665991</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9003,7 +9008,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9013,12 +9018,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Inte jättegamla. Rikligt.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9166,10 +9171,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131824427</v>
+        <v>131822045</v>
       </c>
       <c r="B78" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9177,39 +9182,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497048</v>
+        <v>496716</v>
       </c>
       <c r="R78" t="n">
-        <v>6665991</v>
+        <v>6665704</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Inte jättegamla. Rikligt.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9280,6 +9280,1265 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>131879458</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>496747</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6665556</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>131879299</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>496914</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6666038</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>131879266</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>496903</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6666043</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>131885230</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>496973</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6665937</v>
+      </c>
+      <c r="S82" t="n">
+        <v>50</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Spelande pärlugglehane</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>131879331</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kringelbackarna., Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>496786</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6665976</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>131879441</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>496778</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6665505</v>
+      </c>
+      <c r="S84" t="n">
+        <v>25</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>131879365</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>497270</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6665937</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>131879471</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>496653</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6665540</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>131879491</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>496672</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6665623</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>131879507</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>496662</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6665641</v>
+      </c>
+      <c r="S88" t="n">
+        <v>25</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>131879280</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>496916</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6666046</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>131879417</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>496767</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6665516</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9071-2026 artfynd.xlsx
+++ b/artfynd/A 9071-2026 artfynd.xlsx
@@ -2226,50 +2226,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131817592</v>
+        <v>131813411</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>91795</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497156</v>
+        <v>497031</v>
       </c>
       <c r="R16" t="n">
-        <v>6665625</v>
+        <v>6666011</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2301,7 +2296,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2311,7 +2306,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131813949</v>
+        <v>131825446</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,16 +2344,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2369,7 +2364,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2378,10 +2373,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497132</v>
+        <v>497225</v>
       </c>
       <c r="R17" t="n">
-        <v>6665999</v>
+        <v>6665902</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2418,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Skalad klen gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,45 +2450,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131813411</v>
+        <v>131817592</v>
       </c>
       <c r="B18" t="n">
-        <v>91795</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497031</v>
+        <v>497156</v>
       </c>
       <c r="R18" t="n">
-        <v>6666011</v>
+        <v>6665625</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2520,7 +2525,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2535,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131825446</v>
+        <v>131813949</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,16 +2573,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2588,7 +2593,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2597,10 +2602,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497225</v>
+        <v>497132</v>
       </c>
       <c r="R19" t="n">
-        <v>6665902</v>
+        <v>6665999</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2632,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,12 +2647,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Skalad klen gran.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3779,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131820211</v>
+        <v>131820988</v>
       </c>
       <c r="B30" t="n">
-        <v>79264</v>
+        <v>91853</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3790,34 +3790,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496715</v>
+        <v>496679</v>
       </c>
       <c r="R30" t="n">
-        <v>6665621</v>
+        <v>6665484</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3849,7 +3858,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3859,12 +3868,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3891,32 +3900,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131821816</v>
+        <v>131826218</v>
       </c>
       <c r="B31" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3926,10 +3935,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496659</v>
+        <v>496988</v>
       </c>
       <c r="R31" t="n">
-        <v>6665733</v>
+        <v>6666049</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3961,7 +3970,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3971,12 +3980,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4003,45 +4007,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131821919</v>
+        <v>131812738</v>
       </c>
       <c r="B32" t="n">
-        <v>79264</v>
+        <v>99038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496673</v>
+        <v>497044</v>
       </c>
       <c r="R32" t="n">
-        <v>6665715</v>
+        <v>6666126</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4073,7 +4091,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4083,12 +4101,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4115,7 +4128,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131820461</v>
+        <v>131820211</v>
       </c>
       <c r="B33" t="n">
         <v>79264</v>
@@ -4150,10 +4163,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496750</v>
+        <v>496715</v>
       </c>
       <c r="R33" t="n">
-        <v>6665519</v>
+        <v>6665621</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4185,7 +4198,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4195,7 +4208,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4227,7 +4240,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131822613</v>
+        <v>131821816</v>
       </c>
       <c r="B34" t="n">
         <v>79264</v>
@@ -4262,10 +4275,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496886</v>
+        <v>496659</v>
       </c>
       <c r="R34" t="n">
-        <v>6665791</v>
+        <v>6665733</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4297,7 +4310,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4307,7 +4320,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,7 +4352,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131813256</v>
+        <v>131821919</v>
       </c>
       <c r="B35" t="n">
         <v>79264</v>
@@ -4369,10 +4387,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497050</v>
+        <v>496673</v>
       </c>
       <c r="R35" t="n">
-        <v>6666028</v>
+        <v>6665715</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4404,7 +4422,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4414,7 +4432,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4446,10 +4464,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131813803</v>
+        <v>131820461</v>
       </c>
       <c r="B36" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4457,39 +4475,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497075</v>
+        <v>496750</v>
       </c>
       <c r="R36" t="n">
-        <v>6665986</v>
+        <v>6665519</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4521,7 +4534,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4531,7 +4544,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4558,10 +4576,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131820260</v>
+        <v>131822613</v>
       </c>
       <c r="B37" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4569,39 +4587,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496750</v>
+        <v>496886</v>
       </c>
       <c r="R37" t="n">
-        <v>6665593</v>
+        <v>6665791</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4633,7 +4646,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4643,7 +4656,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4670,59 +4683,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131812738</v>
+        <v>131813256</v>
       </c>
       <c r="B38" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497044</v>
+        <v>497050</v>
       </c>
       <c r="R38" t="n">
-        <v>6666126</v>
+        <v>6666028</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4754,7 +4753,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4764,7 +4763,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4791,10 +4795,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131820988</v>
+        <v>131813803</v>
       </c>
       <c r="B39" t="n">
-        <v>91853</v>
+        <v>57899</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,31 +4806,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496679</v>
+        <v>497075</v>
       </c>
       <c r="R39" t="n">
-        <v>6665484</v>
+        <v>6665986</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4880,12 +4880,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4912,45 +4907,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131826218</v>
+        <v>131820260</v>
       </c>
       <c r="B40" t="n">
-        <v>91795</v>
+        <v>57899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496988</v>
+        <v>496750</v>
       </c>
       <c r="R40" t="n">
-        <v>6666049</v>
+        <v>6665593</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131817253</v>
+        <v>131820286</v>
       </c>
       <c r="B41" t="n">
-        <v>97278</v>
+        <v>79264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5030,34 +5030,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497240</v>
+        <v>496750</v>
       </c>
       <c r="R41" t="n">
-        <v>6665672</v>
+        <v>6665593</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt på låga, naturskogskaraktär. Opåverkat.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5131,10 +5131,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131820286</v>
+        <v>131813324</v>
       </c>
       <c r="B42" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5142,21 +5142,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496750</v>
+        <v>497037</v>
       </c>
       <c r="R42" t="n">
-        <v>6665593</v>
+        <v>6666041</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Möjlig början till bobygge. Tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5243,10 +5243,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131813324</v>
+        <v>131817253</v>
       </c>
       <c r="B43" t="n">
-        <v>57899</v>
+        <v>97278</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5254,34 +5254,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497037</v>
+        <v>497240</v>
       </c>
       <c r="R43" t="n">
-        <v>6666041</v>
+        <v>6665672</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Möjlig början till bobygge. Tall.</t>
+          <t>Rikligt på låga, naturskogskaraktär. Opåverkat.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 9071-2026 artfynd.xlsx
+++ b/artfynd/A 9071-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131819996</v>
+        <v>131815750</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496731</v>
+        <v>497401</v>
       </c>
       <c r="R3" t="n">
-        <v>6665630</v>
+        <v>6665928</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,12 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131824941</v>
+        <v>131819996</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497158</v>
+        <v>496731</v>
       </c>
       <c r="R4" t="n">
-        <v>6665848</v>
+        <v>6665630</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +964,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131826065</v>
+        <v>131824941</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497022</v>
+        <v>497158</v>
       </c>
       <c r="R5" t="n">
-        <v>6666032</v>
+        <v>6665848</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131820483</v>
+        <v>131826065</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496755</v>
+        <v>497022</v>
       </c>
       <c r="R6" t="n">
-        <v>6665498</v>
+        <v>6666032</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131823377</v>
+        <v>131820483</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,19 +1221,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1246,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497013</v>
+        <v>496755</v>
       </c>
       <c r="R7" t="n">
-        <v>6665916</v>
+        <v>6665498</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1281,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1291,7 +1290,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,45 +1322,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131815946</v>
+        <v>131823377</v>
       </c>
       <c r="B8" t="n">
-        <v>91795</v>
+        <v>91858</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497370</v>
+        <v>497013</v>
       </c>
       <c r="R8" t="n">
-        <v>6665890</v>
+        <v>6665916</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131815750</v>
+        <v>131815946</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>91801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497401</v>
+        <v>497370</v>
       </c>
       <c r="R9" t="n">
-        <v>6665928</v>
+        <v>6665890</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,7 +1535,7 @@
         <v>131823127</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>131812867</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,54 +1775,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131817895</v>
+        <v>131813222</v>
       </c>
       <c r="B12" t="n">
-        <v>93120</v>
+        <v>97284</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497114</v>
+        <v>497070</v>
       </c>
       <c r="R12" t="n">
-        <v>6665644</v>
+        <v>6666043</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1854,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131817878</v>
+        <v>131817895</v>
       </c>
       <c r="B13" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1912,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1935,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497115</v>
+        <v>497114</v>
       </c>
       <c r="R13" t="n">
-        <v>6665636</v>
+        <v>6665644</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1971,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +1998,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131813222</v>
+        <v>131817878</v>
       </c>
       <c r="B14" t="n">
-        <v>97278</v>
+        <v>93126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497070</v>
+        <v>497115</v>
       </c>
       <c r="R14" t="n">
-        <v>6666043</v>
+        <v>6665636</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2117,7 @@
         <v>131812941</v>
       </c>
       <c r="B15" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,45 +2226,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131813411</v>
+        <v>131817592</v>
       </c>
       <c r="B16" t="n">
-        <v>91795</v>
+        <v>57901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497031</v>
+        <v>497156</v>
       </c>
       <c r="R16" t="n">
-        <v>6666011</v>
+        <v>6665625</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2296,7 +2301,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2306,7 +2311,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2333,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131825446</v>
+        <v>131813949</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>57901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,16 +2349,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2364,7 +2369,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2373,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497225</v>
+        <v>497132</v>
       </c>
       <c r="R17" t="n">
-        <v>6665902</v>
+        <v>6665999</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,12 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Skalad klen gran.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,50 +2450,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131817592</v>
+        <v>131813411</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>91801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497156</v>
+        <v>497031</v>
       </c>
       <c r="R18" t="n">
-        <v>6665625</v>
+        <v>6666011</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2525,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2535,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131813949</v>
+        <v>131825446</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,16 +2568,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2593,7 +2588,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2602,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497132</v>
+        <v>497225</v>
       </c>
       <c r="R19" t="n">
-        <v>6665999</v>
+        <v>6665902</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2637,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2647,7 +2642,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Skalad klen gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,7 +2677,7 @@
         <v>131820090</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>131820198</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>131822481</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>131822287</v>
       </c>
       <c r="B23" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>131822631</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3224,32 +3224,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131822891</v>
+        <v>131819438</v>
       </c>
       <c r="B25" t="n">
-        <v>91795</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496991</v>
+        <v>496909</v>
       </c>
       <c r="R25" t="n">
-        <v>6665792</v>
+        <v>6665623</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3304,7 +3304,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3331,50 +3336,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131814639</v>
+        <v>131822891</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>91801</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497222</v>
+        <v>496991</v>
       </c>
       <c r="R26" t="n">
-        <v>6665985</v>
+        <v>6665792</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3416,12 +3416,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3448,10 +3443,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131819438</v>
+        <v>131819620</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3483,10 +3478,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496909</v>
+        <v>496839</v>
       </c>
       <c r="R27" t="n">
-        <v>6665623</v>
+        <v>6665620</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3518,7 +3513,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3528,12 +3523,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3560,10 +3555,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131819620</v>
+        <v>131823937</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3595,10 +3590,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496839</v>
+        <v>496961</v>
       </c>
       <c r="R28" t="n">
-        <v>6665620</v>
+        <v>6665968</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3630,7 +3625,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3640,12 +3635,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gran.</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3672,10 +3662,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131823937</v>
+        <v>131814639</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,34 +3673,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496961</v>
+        <v>497222</v>
       </c>
       <c r="R29" t="n">
-        <v>6665968</v>
+        <v>6665985</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3742,7 +3737,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3752,7 +3747,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3779,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131820988</v>
+        <v>131813803</v>
       </c>
       <c r="B30" t="n">
-        <v>91853</v>
+        <v>57901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3790,31 +3790,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3823,10 +3819,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496679</v>
+        <v>497075</v>
       </c>
       <c r="R30" t="n">
-        <v>6665484</v>
+        <v>6665986</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3858,7 +3854,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3868,12 +3864,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3900,45 +3891,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131826218</v>
+        <v>131820260</v>
       </c>
       <c r="B31" t="n">
-        <v>91795</v>
+        <v>57901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496988</v>
+        <v>496750</v>
       </c>
       <c r="R31" t="n">
-        <v>6666049</v>
+        <v>6665593</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3970,7 +3966,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3980,7 +3976,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4007,59 +4003,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131812738</v>
+        <v>131820461</v>
       </c>
       <c r="B32" t="n">
-        <v>99038</v>
+        <v>79266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497044</v>
+        <v>496750</v>
       </c>
       <c r="R32" t="n">
-        <v>6666126</v>
+        <v>6665519</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4091,7 +4073,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4101,7 +4083,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4128,45 +4115,59 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131820211</v>
+        <v>131812738</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>99044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496715</v>
+        <v>497044</v>
       </c>
       <c r="R33" t="n">
-        <v>6665621</v>
+        <v>6666126</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4198,7 +4199,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4208,12 +4209,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4240,10 +4236,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131821816</v>
+        <v>131820211</v>
       </c>
       <c r="B34" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,10 +4271,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496659</v>
+        <v>496715</v>
       </c>
       <c r="R34" t="n">
-        <v>6665733</v>
+        <v>6665621</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4310,7 +4306,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4320,7 +4316,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4352,10 +4348,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131821919</v>
+        <v>131820988</v>
       </c>
       <c r="B35" t="n">
-        <v>79264</v>
+        <v>91859</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,34 +4359,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496673</v>
+        <v>496679</v>
       </c>
       <c r="R35" t="n">
-        <v>6665715</v>
+        <v>6665484</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4422,7 +4427,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4432,12 +4437,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,10 +4469,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131820461</v>
+        <v>131821816</v>
       </c>
       <c r="B36" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4499,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496750</v>
+        <v>496659</v>
       </c>
       <c r="R36" t="n">
-        <v>6665519</v>
+        <v>6665733</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4534,7 +4539,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4544,7 +4549,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4576,10 +4581,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131822613</v>
+        <v>131821919</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4611,10 +4616,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496886</v>
+        <v>496673</v>
       </c>
       <c r="R37" t="n">
-        <v>6665791</v>
+        <v>6665715</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4646,7 +4651,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4656,7 +4661,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4683,32 +4693,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131813256</v>
+        <v>131826218</v>
       </c>
       <c r="B38" t="n">
-        <v>79264</v>
+        <v>91801</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4718,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497050</v>
+        <v>496988</v>
       </c>
       <c r="R38" t="n">
-        <v>6666028</v>
+        <v>6666049</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4753,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4763,12 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4795,10 +4800,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131813803</v>
+        <v>131822613</v>
       </c>
       <c r="B39" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4806,39 +4811,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497075</v>
+        <v>496886</v>
       </c>
       <c r="R39" t="n">
-        <v>6665986</v>
+        <v>6665791</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131820260</v>
+        <v>131813256</v>
       </c>
       <c r="B40" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4918,39 +4918,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496750</v>
+        <v>497050</v>
       </c>
       <c r="R40" t="n">
-        <v>6665593</v>
+        <v>6666028</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4982,7 +4977,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4992,7 +4987,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131820286</v>
+        <v>131817253</v>
       </c>
       <c r="B41" t="n">
-        <v>79264</v>
+        <v>97284</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5030,34 +5030,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496750</v>
+        <v>497240</v>
       </c>
       <c r="R41" t="n">
-        <v>6665593</v>
+        <v>6665672</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Rikligt på låga, naturskogskaraktär. Opåverkat.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5134,7 +5134,7 @@
         <v>131813324</v>
       </c>
       <c r="B42" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,10 +5243,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131817253</v>
+        <v>131820286</v>
       </c>
       <c r="B43" t="n">
-        <v>97278</v>
+        <v>79266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5254,34 +5254,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497240</v>
+        <v>496750</v>
       </c>
       <c r="R43" t="n">
-        <v>6665672</v>
+        <v>6665593</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på låga, naturskogskaraktär. Opåverkat.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5355,10 +5355,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131820420</v>
+        <v>131816700</v>
       </c>
       <c r="B44" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5366,34 +5366,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496739</v>
+        <v>497217</v>
       </c>
       <c r="R44" t="n">
-        <v>6665550</v>
+        <v>6665802</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5425,7 +5430,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5435,12 +5440,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5467,38 +5472,47 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131816700</v>
+        <v>131824551</v>
       </c>
       <c r="B45" t="n">
-        <v>57902</v>
+        <v>99044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5507,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497217</v>
+        <v>497094</v>
       </c>
       <c r="R45" t="n">
-        <v>6665802</v>
+        <v>6665962</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5542,7 +5556,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5552,12 +5566,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5584,59 +5593,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131824551</v>
+        <v>131820420</v>
       </c>
       <c r="B46" t="n">
-        <v>99038</v>
+        <v>79266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497094</v>
+        <v>496739</v>
       </c>
       <c r="R46" t="n">
-        <v>6665962</v>
+        <v>6665550</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5668,7 +5663,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5678,7 +5673,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5705,10 +5705,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131820034</v>
+        <v>131815569</v>
       </c>
       <c r="B47" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5716,34 +5716,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496723</v>
+        <v>497435</v>
       </c>
       <c r="R47" t="n">
-        <v>6665623</v>
+        <v>6665962</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5775,7 +5780,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5785,12 +5790,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5817,10 +5817,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131822460</v>
+        <v>131820034</v>
       </c>
       <c r="B48" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496866</v>
+        <v>496723</v>
       </c>
       <c r="R48" t="n">
-        <v>6665758</v>
+        <v>6665623</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5897,7 +5897,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5924,10 +5929,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131815569</v>
+        <v>131822460</v>
       </c>
       <c r="B49" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5935,39 +5940,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497435</v>
+        <v>496866</v>
       </c>
       <c r="R49" t="n">
-        <v>6665962</v>
+        <v>6665758</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6036,45 +6036,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131823667</v>
+        <v>131814230</v>
       </c>
       <c r="B50" t="n">
-        <v>91832</v>
+        <v>91801</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496999</v>
+        <v>497196</v>
       </c>
       <c r="R50" t="n">
-        <v>6665942</v>
+        <v>6665988</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6143,10 +6143,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131814230</v>
+        <v>131815592</v>
       </c>
       <c r="B51" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497196</v>
+        <v>497422</v>
       </c>
       <c r="R51" t="n">
-        <v>6665988</v>
+        <v>6665955</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6250,45 +6250,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131815592</v>
+        <v>131823667</v>
       </c>
       <c r="B52" t="n">
-        <v>91795</v>
+        <v>91838</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497422</v>
+        <v>496999</v>
       </c>
       <c r="R52" t="n">
-        <v>6665955</v>
+        <v>6665942</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6357,50 +6357,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131814218</v>
+        <v>131820897</v>
       </c>
       <c r="B53" t="n">
-        <v>57899</v>
+        <v>5178</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497196</v>
+        <v>496659</v>
       </c>
       <c r="R53" t="n">
-        <v>6665980</v>
+        <v>6665450</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6469,10 +6469,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131816009</v>
+        <v>131816514</v>
       </c>
       <c r="B54" t="n">
-        <v>57899</v>
+        <v>57904</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6480,16 +6480,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497376</v>
+        <v>497264</v>
       </c>
       <c r="R54" t="n">
-        <v>6665876</v>
+        <v>6665784</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6554,7 +6554,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6584,7 +6589,7 @@
         <v>131819420</v>
       </c>
       <c r="B55" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6693,50 +6698,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131820897</v>
+        <v>131816009</v>
       </c>
       <c r="B56" t="n">
-        <v>5178</v>
+        <v>57901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496659</v>
+        <v>497376</v>
       </c>
       <c r="R56" t="n">
-        <v>6665450</v>
+        <v>6665876</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6768,7 +6773,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6778,7 +6783,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6805,10 +6810,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131816514</v>
+        <v>131814218</v>
       </c>
       <c r="B57" t="n">
-        <v>57902</v>
+        <v>57901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6816,16 +6821,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6836,7 +6841,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6845,10 +6850,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497264</v>
+        <v>497196</v>
       </c>
       <c r="R57" t="n">
-        <v>6665784</v>
+        <v>6665980</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6880,7 +6885,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6890,12 +6895,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6925,7 +6925,7 @@
         <v>131825046</v>
       </c>
       <c r="B58" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>131819462</v>
       </c>
       <c r="B59" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7253,50 +7253,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131812974</v>
+        <v>131814895</v>
       </c>
       <c r="B61" t="n">
-        <v>99038</v>
+        <v>79266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497066</v>
+        <v>497309</v>
       </c>
       <c r="R61" t="n">
-        <v>6666099</v>
+        <v>6666024</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7328,7 +7323,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7338,7 +7333,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7365,45 +7365,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131814895</v>
+        <v>131812974</v>
       </c>
       <c r="B62" t="n">
-        <v>79264</v>
+        <v>99044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497309</v>
+        <v>497066</v>
       </c>
       <c r="R62" t="n">
-        <v>6666024</v>
+        <v>6666099</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7435,7 +7440,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7445,12 +7450,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Gran.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7480,7 +7480,7 @@
         <v>131823511</v>
       </c>
       <c r="B63" t="n">
-        <v>91846</v>
+        <v>91852</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7584,10 +7584,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131820394</v>
+        <v>131824196</v>
       </c>
       <c r="B64" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7595,34 +7595,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496729</v>
+        <v>497013</v>
       </c>
       <c r="R64" t="n">
-        <v>6665578</v>
+        <v>6665983</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7654,7 +7659,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7664,12 +7669,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Barkfläk, flera barkborre skadade granar. Hagelsvärm.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7699,7 +7704,7 @@
         <v>131813681</v>
       </c>
       <c r="B65" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7813,10 +7818,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131824196</v>
+        <v>131820394</v>
       </c>
       <c r="B66" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7824,39 +7829,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497013</v>
+        <v>496729</v>
       </c>
       <c r="R66" t="n">
-        <v>6665983</v>
+        <v>6665578</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7898,12 +7898,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Barkfläk, flera barkborre skadade granar. Hagelsvärm.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7930,10 +7930,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131822008</v>
+        <v>131820687</v>
       </c>
       <c r="B67" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7941,34 +7941,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496703</v>
+        <v>496727</v>
       </c>
       <c r="R67" t="n">
-        <v>6665712</v>
+        <v>6665448</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8000,7 +8005,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8010,12 +8015,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8042,10 +8042,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131821003</v>
+        <v>131817993</v>
       </c>
       <c r="B68" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8053,34 +8053,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496677</v>
+        <v>497109</v>
       </c>
       <c r="R68" t="n">
-        <v>6665493</v>
+        <v>6665663</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8112,7 +8117,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8122,12 +8127,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Färska och äldre.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8154,10 +8159,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131820687</v>
+        <v>131820601</v>
       </c>
       <c r="B69" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8185,7 +8190,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8194,10 +8199,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496727</v>
+        <v>496774</v>
       </c>
       <c r="R69" t="n">
-        <v>6665448</v>
+        <v>6665442</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8229,7 +8234,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8239,7 +8244,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Gammal tall, inte jätte gammalt hål.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8266,10 +8276,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131817993</v>
+        <v>131813190</v>
       </c>
       <c r="B70" t="n">
-        <v>57899</v>
+        <v>97284</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8277,39 +8287,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497109</v>
+        <v>497078</v>
       </c>
       <c r="R70" t="n">
-        <v>6665663</v>
+        <v>6666034</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8341,7 +8346,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8351,12 +8356,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska och äldre.</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8383,10 +8383,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131820601</v>
+        <v>131822008</v>
       </c>
       <c r="B71" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8394,39 +8394,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496774</v>
+        <v>496703</v>
       </c>
       <c r="R71" t="n">
-        <v>6665442</v>
+        <v>6665712</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8468,12 +8463,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Gammal tall, inte jätte gammalt hål.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8500,10 +8495,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131813190</v>
+        <v>131821003</v>
       </c>
       <c r="B72" t="n">
-        <v>97278</v>
+        <v>79266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8511,34 +8506,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497078</v>
+        <v>496677</v>
       </c>
       <c r="R72" t="n">
-        <v>6666034</v>
+        <v>6665493</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8570,7 +8565,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8580,7 +8575,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8610,7 +8610,7 @@
         <v>131814741</v>
       </c>
       <c r="B73" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>131825840</v>
       </c>
       <c r="B74" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8821,10 +8821,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131823795</v>
+        <v>131822045</v>
       </c>
       <c r="B75" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8832,21 +8832,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496953</v>
+        <v>496716</v>
       </c>
       <c r="R75" t="n">
-        <v>6665935</v>
+        <v>6665704</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Barkfläk, mycket små flagor under träd.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8933,38 +8933,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131824427</v>
+        <v>131822816</v>
       </c>
       <c r="B76" t="n">
-        <v>57902</v>
+        <v>93126</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8973,10 +8977,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497048</v>
+        <v>496977</v>
       </c>
       <c r="R76" t="n">
-        <v>6665991</v>
+        <v>6665784</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9008,7 +9012,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9018,12 +9022,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Inte jättegamla. Rikligt.</t>
+          <t>Intill kolbotten</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9050,54 +9054,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131822816</v>
+        <v>131823795</v>
       </c>
       <c r="B77" t="n">
-        <v>93120</v>
+        <v>57904</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496977</v>
+        <v>496953</v>
       </c>
       <c r="R77" t="n">
-        <v>6665784</v>
+        <v>6665935</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9129,7 +9124,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9139,12 +9134,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Intill kolbotten</t>
+          <t>Barkfläk, mycket små flagor under träd.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9171,10 +9166,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131822045</v>
+        <v>131824427</v>
       </c>
       <c r="B78" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9182,34 +9177,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496716</v>
+        <v>497048</v>
       </c>
       <c r="R78" t="n">
-        <v>6665704</v>
+        <v>6665991</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Inte jättegamla. Rikligt.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9286,7 +9286,7 @@
         <v>131879458</v>
       </c>
       <c r="B79" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>131879299</v>
       </c>
       <c r="B80" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>131879266</v>
       </c>
       <c r="B81" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>131885230</v>
       </c>
       <c r="B82" t="n">
-        <v>57734</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>131879331</v>
       </c>
       <c r="B83" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>131879441</v>
       </c>
       <c r="B84" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>131879365</v>
       </c>
       <c r="B85" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>131879471</v>
       </c>
       <c r="B86" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>131879491</v>
       </c>
       <c r="B87" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>131879507</v>
       </c>
       <c r="B88" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>131879280</v>
       </c>
       <c r="B89" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>131879417</v>
       </c>
       <c r="B90" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 9071-2026 artfynd.xlsx
+++ b/artfynd/A 9071-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131815750</v>
+        <v>131819996</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497401</v>
+        <v>496731</v>
       </c>
       <c r="R3" t="n">
-        <v>6665928</v>
+        <v>6665630</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131819996</v>
+        <v>131824941</v>
       </c>
       <c r="B4" t="n">
         <v>79266</v>
@@ -915,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496731</v>
+        <v>497158</v>
       </c>
       <c r="R4" t="n">
-        <v>6665630</v>
+        <v>6665848</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -954,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131824941</v>
+        <v>131826065</v>
       </c>
       <c r="B5" t="n">
         <v>79266</v>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497158</v>
+        <v>497022</v>
       </c>
       <c r="R5" t="n">
-        <v>6665848</v>
+        <v>6666032</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131826065</v>
+        <v>131820483</v>
       </c>
       <c r="B6" t="n">
         <v>79266</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497022</v>
+        <v>496755</v>
       </c>
       <c r="R6" t="n">
-        <v>6666032</v>
+        <v>6665498</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131820483</v>
+        <v>131823377</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>91858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,23 +1226,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1245,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496755</v>
+        <v>497013</v>
       </c>
       <c r="R7" t="n">
-        <v>6665498</v>
+        <v>6665916</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1281,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,12 +1291,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,41 +1318,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131823377</v>
+        <v>131815946</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>91801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497013</v>
+        <v>497370</v>
       </c>
       <c r="R8" t="n">
-        <v>6665916</v>
+        <v>6665890</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131815946</v>
+        <v>131815750</v>
       </c>
       <c r="B9" t="n">
-        <v>91801</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497370</v>
+        <v>497401</v>
       </c>
       <c r="R9" t="n">
-        <v>6665890</v>
+        <v>6665928</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1775,45 +1775,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131813222</v>
+        <v>131817895</v>
       </c>
       <c r="B12" t="n">
-        <v>97284</v>
+        <v>93126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497070</v>
+        <v>497114</v>
       </c>
       <c r="R12" t="n">
-        <v>6666043</v>
+        <v>6665644</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1845,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1864,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,54 +1891,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131817895</v>
+        <v>131812941</v>
       </c>
       <c r="B13" t="n">
-        <v>93126</v>
+        <v>99044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497114</v>
+        <v>497063</v>
       </c>
       <c r="R13" t="n">
-        <v>6665644</v>
+        <v>6666103</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1961,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,54 +2003,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131817878</v>
+        <v>131813222</v>
       </c>
       <c r="B14" t="n">
-        <v>93126</v>
+        <v>97284</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497115</v>
+        <v>497070</v>
       </c>
       <c r="R14" t="n">
-        <v>6665636</v>
+        <v>6666043</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2077,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,50 +2110,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131812941</v>
+        <v>131817878</v>
       </c>
       <c r="B15" t="n">
-        <v>99044</v>
+        <v>93126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497063</v>
+        <v>497115</v>
       </c>
       <c r="R15" t="n">
-        <v>6666103</v>
+        <v>6665636</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131822481</v>
+        <v>131822631</v>
       </c>
       <c r="B22" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,31 +2899,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496867</v>
+        <v>496916</v>
       </c>
       <c r="R22" t="n">
         <v>6665758</v>
@@ -2958,7 +2963,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2968,7 +2973,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2995,7 +3005,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131822287</v>
+        <v>131822481</v>
       </c>
       <c r="B23" t="n">
         <v>79266</v>
@@ -3030,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496800</v>
+        <v>496867</v>
       </c>
       <c r="R23" t="n">
-        <v>6665757</v>
+        <v>6665758</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3065,7 +3075,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3075,12 +3085,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3107,10 +3112,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131822631</v>
+        <v>131822287</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,39 +3123,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496916</v>
+        <v>496800</v>
       </c>
       <c r="R24" t="n">
-        <v>6665758</v>
+        <v>6665757</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5355,10 +5355,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131816700</v>
+        <v>131820420</v>
       </c>
       <c r="B44" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5366,39 +5366,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497217</v>
+        <v>496739</v>
       </c>
       <c r="R44" t="n">
-        <v>6665802</v>
+        <v>6665550</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5430,7 +5425,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5440,12 +5435,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5472,47 +5467,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131824551</v>
+        <v>131816700</v>
       </c>
       <c r="B45" t="n">
-        <v>99044</v>
+        <v>57904</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5521,10 +5507,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497094</v>
+        <v>497217</v>
       </c>
       <c r="R45" t="n">
-        <v>6665962</v>
+        <v>6665802</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5556,7 +5542,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5566,7 +5552,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5593,45 +5584,59 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131820420</v>
+        <v>131824551</v>
       </c>
       <c r="B46" t="n">
-        <v>79266</v>
+        <v>99044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496739</v>
+        <v>497094</v>
       </c>
       <c r="R46" t="n">
-        <v>6665550</v>
+        <v>6665962</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5663,7 +5668,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5673,12 +5678,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6357,50 +6357,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131820897</v>
+        <v>131814218</v>
       </c>
       <c r="B53" t="n">
-        <v>5178</v>
+        <v>57901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496659</v>
+        <v>497196</v>
       </c>
       <c r="R53" t="n">
-        <v>6665450</v>
+        <v>6665980</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6469,10 +6469,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131816514</v>
+        <v>131819420</v>
       </c>
       <c r="B54" t="n">
-        <v>57904</v>
+        <v>57901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6480,16 +6480,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6500,19 +6500,19 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497264</v>
+        <v>496910</v>
       </c>
       <c r="R54" t="n">
-        <v>6665784</v>
+        <v>6665624</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6554,12 +6554,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6586,7 +6581,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131819420</v>
+        <v>131816009</v>
       </c>
       <c r="B55" t="n">
         <v>57901</v>
@@ -6617,19 +6612,19 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496910</v>
+        <v>497376</v>
       </c>
       <c r="R55" t="n">
-        <v>6665624</v>
+        <v>6665876</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6661,7 +6656,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6671,7 +6666,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6698,50 +6693,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131816009</v>
+        <v>131820897</v>
       </c>
       <c r="B56" t="n">
-        <v>57901</v>
+        <v>5178</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497376</v>
+        <v>496659</v>
       </c>
       <c r="R56" t="n">
-        <v>6665876</v>
+        <v>6665450</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6773,7 +6768,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6783,7 +6778,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6810,10 +6805,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131814218</v>
+        <v>131816514</v>
       </c>
       <c r="B57" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6821,16 +6816,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6841,7 +6836,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6850,10 +6845,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497196</v>
+        <v>497264</v>
       </c>
       <c r="R57" t="n">
-        <v>6665980</v>
+        <v>6665784</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6885,7 +6880,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6895,7 +6890,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -9485,27 +9485,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131879266</v>
+        <v>131885230</v>
       </c>
       <c r="B81" t="n">
-        <v>57904</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>102622</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9514,27 +9514,34 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496903</v>
+        <v>496973</v>
       </c>
       <c r="R81" t="n">
-        <v>6666043</v>
+        <v>6665937</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9558,17 +9565,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Spelande pärlugglehane</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9583,39 +9600,39 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131885230</v>
+        <v>131879266</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>57904</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102622</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9624,34 +9641,27 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496973</v>
+        <v>496903</v>
       </c>
       <c r="R82" t="n">
-        <v>6665937</v>
+        <v>6666043</v>
       </c>
       <c r="S82" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9675,27 +9685,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Spelande pärlugglehane</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9710,12 +9710,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9823,37 +9823,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131879441</v>
+        <v>131879365</v>
       </c>
       <c r="B84" t="n">
-        <v>79266</v>
+        <v>57092</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9861,10 +9866,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496778</v>
+        <v>497270</v>
       </c>
       <c r="R84" t="n">
-        <v>6665505</v>
+        <v>6665937</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9905,7 +9910,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9924,42 +9928,37 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131879365</v>
+        <v>131879441</v>
       </c>
       <c r="B85" t="n">
-        <v>57092</v>
+        <v>79266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9967,10 +9966,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497270</v>
+        <v>496778</v>
       </c>
       <c r="R85" t="n">
-        <v>6665937</v>
+        <v>6665505</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10011,6 +10010,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9071-2026 artfynd.xlsx
+++ b/artfynd/A 9071-2026 artfynd.xlsx
@@ -1775,54 +1775,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131817895</v>
+        <v>131813222</v>
       </c>
       <c r="B12" t="n">
-        <v>93126</v>
+        <v>97284</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497114</v>
+        <v>497070</v>
       </c>
       <c r="R12" t="n">
-        <v>6665644</v>
+        <v>6666043</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1854,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,50 +1882,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131812941</v>
+        <v>131817895</v>
       </c>
       <c r="B13" t="n">
-        <v>99044</v>
+        <v>93126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497063</v>
+        <v>497114</v>
       </c>
       <c r="R13" t="n">
-        <v>6666103</v>
+        <v>6665644</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1966,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1971,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,45 +1998,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131813222</v>
+        <v>131817878</v>
       </c>
       <c r="B14" t="n">
-        <v>97284</v>
+        <v>93126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497070</v>
+        <v>497115</v>
       </c>
       <c r="R14" t="n">
-        <v>6666043</v>
+        <v>6665636</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,54 +2114,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131817878</v>
+        <v>131812941</v>
       </c>
       <c r="B15" t="n">
-        <v>93126</v>
+        <v>99044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497115</v>
+        <v>497063</v>
       </c>
       <c r="R15" t="n">
-        <v>6665636</v>
+        <v>6666103</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131822631</v>
+        <v>131822481</v>
       </c>
       <c r="B22" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,36 +2899,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496916</v>
+        <v>496867</v>
       </c>
       <c r="R22" t="n">
         <v>6665758</v>
@@ -2963,7 +2958,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2973,12 +2968,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3005,7 +2995,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131822481</v>
+        <v>131822287</v>
       </c>
       <c r="B23" t="n">
         <v>79266</v>
@@ -3040,10 +3030,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496867</v>
+        <v>496800</v>
       </c>
       <c r="R23" t="n">
-        <v>6665758</v>
+        <v>6665757</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3075,7 +3065,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3085,7 +3075,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3112,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131822287</v>
+        <v>131822631</v>
       </c>
       <c r="B24" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3123,34 +3118,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496800</v>
+        <v>496916</v>
       </c>
       <c r="R24" t="n">
-        <v>6665757</v>
+        <v>6665758</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4003,7 +4003,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131820461</v>
+        <v>131820211</v>
       </c>
       <c r="B32" t="n">
         <v>79266</v>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496750</v>
+        <v>496715</v>
       </c>
       <c r="R32" t="n">
-        <v>6665519</v>
+        <v>6665621</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4115,47 +4115,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131812738</v>
+        <v>131820988</v>
       </c>
       <c r="B33" t="n">
-        <v>99044</v>
+        <v>91859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4164,10 +4159,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497044</v>
+        <v>496679</v>
       </c>
       <c r="R33" t="n">
-        <v>6666126</v>
+        <v>6665484</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4199,7 +4194,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4209,7 +4204,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4236,7 +4236,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131820211</v>
+        <v>131821816</v>
       </c>
       <c r="B34" t="n">
         <v>79266</v>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496715</v>
+        <v>496659</v>
       </c>
       <c r="R34" t="n">
-        <v>6665621</v>
+        <v>6665733</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4348,10 +4348,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131820988</v>
+        <v>131821919</v>
       </c>
       <c r="B35" t="n">
-        <v>91859</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,43 +4359,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496679</v>
+        <v>496673</v>
       </c>
       <c r="R35" t="n">
-        <v>6665484</v>
+        <v>6665715</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4427,7 +4418,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4437,12 +4428,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,32 +4460,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131821816</v>
+        <v>131826218</v>
       </c>
       <c r="B36" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4504,10 +4495,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496659</v>
+        <v>496988</v>
       </c>
       <c r="R36" t="n">
-        <v>6665733</v>
+        <v>6666049</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4539,7 +4530,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4549,12 +4540,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4581,7 +4567,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131821919</v>
+        <v>131820461</v>
       </c>
       <c r="B37" t="n">
         <v>79266</v>
@@ -4616,10 +4602,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496673</v>
+        <v>496750</v>
       </c>
       <c r="R37" t="n">
-        <v>6665715</v>
+        <v>6665519</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4651,7 +4637,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4661,7 +4647,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4693,32 +4679,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131826218</v>
+        <v>131822613</v>
       </c>
       <c r="B38" t="n">
-        <v>91801</v>
+        <v>79266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,10 +4714,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496988</v>
+        <v>496886</v>
       </c>
       <c r="R38" t="n">
-        <v>6666049</v>
+        <v>6665791</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4763,7 +4749,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4773,7 +4759,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,7 +4786,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131822613</v>
+        <v>131813256</v>
       </c>
       <c r="B39" t="n">
         <v>79266</v>
@@ -4835,10 +4821,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496886</v>
+        <v>497050</v>
       </c>
       <c r="R39" t="n">
-        <v>6665791</v>
+        <v>6666028</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4870,7 +4856,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4880,7 +4866,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4907,45 +4898,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131813256</v>
+        <v>131812738</v>
       </c>
       <c r="B40" t="n">
-        <v>79266</v>
+        <v>99044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497050</v>
+        <v>497044</v>
       </c>
       <c r="R40" t="n">
-        <v>6666028</v>
+        <v>6666126</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4977,7 +4982,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4987,12 +4992,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5705,10 +5705,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131815569</v>
+        <v>131820034</v>
       </c>
       <c r="B47" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5716,39 +5716,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497435</v>
+        <v>496723</v>
       </c>
       <c r="R47" t="n">
-        <v>6665962</v>
+        <v>6665623</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5780,7 +5775,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5790,7 +5785,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5817,7 +5817,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131820034</v>
+        <v>131822460</v>
       </c>
       <c r="B48" t="n">
         <v>79266</v>
@@ -5852,10 +5852,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496723</v>
+        <v>496866</v>
       </c>
       <c r="R48" t="n">
-        <v>6665623</v>
+        <v>6665758</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5897,12 +5897,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5929,10 +5924,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131822460</v>
+        <v>131815569</v>
       </c>
       <c r="B49" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5940,34 +5935,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496866</v>
+        <v>497435</v>
       </c>
       <c r="R49" t="n">
-        <v>6665758</v>
+        <v>6665962</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6357,50 +6357,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131814218</v>
+        <v>131820897</v>
       </c>
       <c r="B53" t="n">
-        <v>57901</v>
+        <v>5178</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497196</v>
+        <v>496659</v>
       </c>
       <c r="R53" t="n">
-        <v>6665980</v>
+        <v>6665450</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6469,10 +6469,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131819420</v>
+        <v>131816514</v>
       </c>
       <c r="B54" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6480,16 +6480,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6500,19 +6500,19 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496910</v>
+        <v>497264</v>
       </c>
       <c r="R54" t="n">
-        <v>6665624</v>
+        <v>6665784</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6554,7 +6554,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6581,7 +6586,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131816009</v>
+        <v>131819420</v>
       </c>
       <c r="B55" t="n">
         <v>57901</v>
@@ -6612,19 +6617,19 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497376</v>
+        <v>496910</v>
       </c>
       <c r="R55" t="n">
-        <v>6665876</v>
+        <v>6665624</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6656,7 +6661,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6666,7 +6671,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6693,50 +6698,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131820897</v>
+        <v>131816009</v>
       </c>
       <c r="B56" t="n">
-        <v>5178</v>
+        <v>57901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496659</v>
+        <v>497376</v>
       </c>
       <c r="R56" t="n">
-        <v>6665450</v>
+        <v>6665876</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6768,7 +6773,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6778,7 +6783,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6805,10 +6810,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131816514</v>
+        <v>131814218</v>
       </c>
       <c r="B57" t="n">
-        <v>57904</v>
+        <v>57901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6816,16 +6821,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6836,7 +6841,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6845,10 +6850,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497264</v>
+        <v>497196</v>
       </c>
       <c r="R57" t="n">
-        <v>6665784</v>
+        <v>6665980</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6880,7 +6885,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6890,12 +6895,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7930,10 +7930,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131820687</v>
+        <v>131813190</v>
       </c>
       <c r="B67" t="n">
-        <v>57901</v>
+        <v>97284</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7941,39 +7941,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496727</v>
+        <v>497078</v>
       </c>
       <c r="R67" t="n">
-        <v>6665448</v>
+        <v>6666034</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8005,7 +8000,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8015,7 +8010,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8042,10 +8037,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131817993</v>
+        <v>131822008</v>
       </c>
       <c r="B68" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8053,39 +8048,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497109</v>
+        <v>496703</v>
       </c>
       <c r="R68" t="n">
-        <v>6665663</v>
+        <v>6665712</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8117,7 +8107,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8127,12 +8117,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Färska och äldre.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8159,10 +8149,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131820601</v>
+        <v>131821003</v>
       </c>
       <c r="B69" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8170,39 +8160,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496774</v>
+        <v>496677</v>
       </c>
       <c r="R69" t="n">
-        <v>6665442</v>
+        <v>6665493</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8234,7 +8219,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8244,12 +8229,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Gammal tall, inte jätte gammalt hål.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8276,10 +8261,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131813190</v>
+        <v>131820687</v>
       </c>
       <c r="B70" t="n">
-        <v>97284</v>
+        <v>57901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8287,34 +8272,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497078</v>
+        <v>496727</v>
       </c>
       <c r="R70" t="n">
-        <v>6666034</v>
+        <v>6665448</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8346,7 +8336,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8356,7 +8346,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8383,10 +8373,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131822008</v>
+        <v>131817993</v>
       </c>
       <c r="B71" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8394,34 +8384,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496703</v>
+        <v>497109</v>
       </c>
       <c r="R71" t="n">
-        <v>6665712</v>
+        <v>6665663</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8453,7 +8448,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8463,12 +8458,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Färska och äldre.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8495,10 +8490,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131821003</v>
+        <v>131820601</v>
       </c>
       <c r="B72" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8506,34 +8501,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496677</v>
+        <v>496774</v>
       </c>
       <c r="R72" t="n">
-        <v>6665493</v>
+        <v>6665442</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Gammal tall, inte jätte gammalt hål.</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 9071-2026 artfynd.xlsx
+++ b/artfynd/A 9071-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131819996</v>
+        <v>131815750</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496731</v>
+        <v>497401</v>
       </c>
       <c r="R3" t="n">
-        <v>6665630</v>
+        <v>6665928</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,12 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131824941</v>
+        <v>131819996</v>
       </c>
       <c r="B4" t="n">
         <v>79266</v>
@@ -920,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497158</v>
+        <v>496731</v>
       </c>
       <c r="R4" t="n">
-        <v>6665848</v>
+        <v>6665630</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +964,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131826065</v>
+        <v>131824941</v>
       </c>
       <c r="B5" t="n">
         <v>79266</v>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497022</v>
+        <v>497158</v>
       </c>
       <c r="R5" t="n">
-        <v>6666032</v>
+        <v>6665848</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131820483</v>
+        <v>131826065</v>
       </c>
       <c r="B6" t="n">
         <v>79266</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496755</v>
+        <v>497022</v>
       </c>
       <c r="R6" t="n">
-        <v>6665498</v>
+        <v>6666032</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131823377</v>
+        <v>131820483</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,19 +1221,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1246,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497013</v>
+        <v>496755</v>
       </c>
       <c r="R7" t="n">
-        <v>6665916</v>
+        <v>6665498</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1281,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1291,7 +1290,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,45 +1322,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131815946</v>
+        <v>131823377</v>
       </c>
       <c r="B8" t="n">
-        <v>91801</v>
+        <v>91858</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497370</v>
+        <v>497013</v>
       </c>
       <c r="R8" t="n">
-        <v>6665890</v>
+        <v>6665916</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,32 +1425,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131815750</v>
+        <v>131815946</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>91801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497401</v>
+        <v>497370</v>
       </c>
       <c r="R9" t="n">
-        <v>6665928</v>
+        <v>6665890</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -5131,10 +5131,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131813324</v>
+        <v>131820286</v>
       </c>
       <c r="B42" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5142,21 +5142,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497037</v>
+        <v>496750</v>
       </c>
       <c r="R42" t="n">
-        <v>6666041</v>
+        <v>6665593</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Möjlig början till bobygge. Tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5243,10 +5243,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131820286</v>
+        <v>131813324</v>
       </c>
       <c r="B43" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5254,21 +5254,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496750</v>
+        <v>497037</v>
       </c>
       <c r="R43" t="n">
-        <v>6665593</v>
+        <v>6666041</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Möjlig början till bobygge. Tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -7930,10 +7930,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131813190</v>
+        <v>131820687</v>
       </c>
       <c r="B67" t="n">
-        <v>97284</v>
+        <v>57901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7941,34 +7941,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497078</v>
+        <v>496727</v>
       </c>
       <c r="R67" t="n">
-        <v>6666034</v>
+        <v>6665448</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8000,7 +8005,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8010,7 +8015,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8037,10 +8042,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131822008</v>
+        <v>131817993</v>
       </c>
       <c r="B68" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8048,34 +8053,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496703</v>
+        <v>497109</v>
       </c>
       <c r="R68" t="n">
-        <v>6665712</v>
+        <v>6665663</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8107,7 +8117,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8117,12 +8127,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Färska och äldre.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8149,10 +8159,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131821003</v>
+        <v>131820601</v>
       </c>
       <c r="B69" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8160,34 +8170,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496677</v>
+        <v>496774</v>
       </c>
       <c r="R69" t="n">
-        <v>6665493</v>
+        <v>6665442</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8219,7 +8234,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8229,12 +8244,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Gammal tall, inte jätte gammalt hål.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8261,10 +8276,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131820687</v>
+        <v>131813190</v>
       </c>
       <c r="B70" t="n">
-        <v>57901</v>
+        <v>97284</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8272,39 +8287,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+          <t>Saxberget, Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496727</v>
+        <v>497078</v>
       </c>
       <c r="R70" t="n">
-        <v>6665448</v>
+        <v>6666034</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8336,7 +8346,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8346,7 +8356,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8373,10 +8383,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131817993</v>
+        <v>131822008</v>
       </c>
       <c r="B71" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8384,39 +8394,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Saxberget, Saxberget, Dlr</t>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497109</v>
+        <v>496703</v>
       </c>
       <c r="R71" t="n">
-        <v>6665663</v>
+        <v>6665712</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8448,7 +8453,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8458,12 +8463,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska och äldre.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8490,10 +8495,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131820601</v>
+        <v>131821003</v>
       </c>
       <c r="B72" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8501,39 +8506,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496774</v>
+        <v>496677</v>
       </c>
       <c r="R72" t="n">
-        <v>6665442</v>
+        <v>6665493</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Gammal tall, inte jätte gammalt hål.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9823,42 +9823,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131879365</v>
+        <v>131879441</v>
       </c>
       <c r="B84" t="n">
-        <v>57092</v>
+        <v>79266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9866,10 +9861,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497270</v>
+        <v>496778</v>
       </c>
       <c r="R84" t="n">
-        <v>6665937</v>
+        <v>6665505</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9910,6 +9905,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9928,37 +9924,42 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131879441</v>
+        <v>131879365</v>
       </c>
       <c r="B85" t="n">
-        <v>79266</v>
+        <v>57092</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9966,10 +9967,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>496778</v>
+        <v>497270</v>
       </c>
       <c r="R85" t="n">
-        <v>6665505</v>
+        <v>6665937</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10010,7 +10011,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9071-2026 artfynd.xlsx
+++ b/artfynd/A 9071-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131822481</v>
+        <v>131822631</v>
       </c>
       <c r="B22" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,31 +2899,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496867</v>
+        <v>496916</v>
       </c>
       <c r="R22" t="n">
         <v>6665758</v>
@@ -2958,7 +2963,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2968,7 +2973,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2995,7 +3005,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131822287</v>
+        <v>131822481</v>
       </c>
       <c r="B23" t="n">
         <v>79266</v>
@@ -3030,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496800</v>
+        <v>496867</v>
       </c>
       <c r="R23" t="n">
-        <v>6665757</v>
+        <v>6665758</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3065,7 +3075,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3075,12 +3085,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3107,10 +3112,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131822631</v>
+        <v>131822287</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,39 +3123,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496916</v>
+        <v>496800</v>
       </c>
       <c r="R24" t="n">
-        <v>6665758</v>
+        <v>6665757</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4003,7 +4003,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131820211</v>
+        <v>131820461</v>
       </c>
       <c r="B32" t="n">
         <v>79266</v>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496715</v>
+        <v>496750</v>
       </c>
       <c r="R32" t="n">
-        <v>6665621</v>
+        <v>6665519</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4115,42 +4115,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131820988</v>
+        <v>131812738</v>
       </c>
       <c r="B33" t="n">
-        <v>91859</v>
+        <v>99044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4159,10 +4164,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496679</v>
+        <v>497044</v>
       </c>
       <c r="R33" t="n">
-        <v>6665484</v>
+        <v>6666126</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4194,7 +4199,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4204,12 +4209,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4236,7 +4236,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131821816</v>
+        <v>131820211</v>
       </c>
       <c r="B34" t="n">
         <v>79266</v>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496659</v>
+        <v>496715</v>
       </c>
       <c r="R34" t="n">
-        <v>6665733</v>
+        <v>6665621</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4348,10 +4348,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131821919</v>
+        <v>131820988</v>
       </c>
       <c r="B35" t="n">
-        <v>79266</v>
+        <v>91859</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,34 +4359,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496673</v>
+        <v>496679</v>
       </c>
       <c r="R35" t="n">
-        <v>6665715</v>
+        <v>6665484</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4418,7 +4427,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4428,12 +4437,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Väldigt gamla tallar, garanterat en bit över 200år.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4460,32 +4469,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131826218</v>
+        <v>131821816</v>
       </c>
       <c r="B36" t="n">
-        <v>91801</v>
+        <v>79266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4495,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496988</v>
+        <v>496659</v>
       </c>
       <c r="R36" t="n">
-        <v>6666049</v>
+        <v>6665733</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4530,7 +4539,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4540,7 +4549,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4567,7 +4581,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131820461</v>
+        <v>131821919</v>
       </c>
       <c r="B37" t="n">
         <v>79266</v>
@@ -4602,10 +4616,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496750</v>
+        <v>496673</v>
       </c>
       <c r="R37" t="n">
-        <v>6665519</v>
+        <v>6665715</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4637,7 +4651,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4647,7 +4661,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4679,32 +4693,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131822613</v>
+        <v>131826218</v>
       </c>
       <c r="B38" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4714,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496886</v>
+        <v>496988</v>
       </c>
       <c r="R38" t="n">
-        <v>6665791</v>
+        <v>6666049</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4749,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4759,7 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4786,7 +4800,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131813256</v>
+        <v>131822613</v>
       </c>
       <c r="B39" t="n">
         <v>79266</v>
@@ -4821,10 +4835,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497050</v>
+        <v>496886</v>
       </c>
       <c r="R39" t="n">
-        <v>6666028</v>
+        <v>6665791</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4856,7 +4870,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4866,12 +4880,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,59 +4907,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131812738</v>
+        <v>131813256</v>
       </c>
       <c r="B40" t="n">
-        <v>99044</v>
+        <v>79266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497044</v>
+        <v>497050</v>
       </c>
       <c r="R40" t="n">
-        <v>6666126</v>
+        <v>6666028</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4982,7 +4977,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4992,7 +4987,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5131,10 +5131,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131820286</v>
+        <v>131813324</v>
       </c>
       <c r="B42" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5142,21 +5142,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496750</v>
+        <v>497037</v>
       </c>
       <c r="R42" t="n">
-        <v>6665593</v>
+        <v>6666041</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Möjlig början till bobygge. Tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5243,10 +5243,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131813324</v>
+        <v>131820286</v>
       </c>
       <c r="B43" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5254,21 +5254,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497037</v>
+        <v>496750</v>
       </c>
       <c r="R43" t="n">
-        <v>6666041</v>
+        <v>6665593</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Möjlig början till bobygge. Tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -7584,10 +7584,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131824196</v>
+        <v>131820394</v>
       </c>
       <c r="B64" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7595,39 +7595,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497013</v>
+        <v>496729</v>
       </c>
       <c r="R64" t="n">
-        <v>6665983</v>
+        <v>6665578</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7659,7 +7654,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7669,12 +7664,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Barkfläk, flera barkborre skadade granar. Hagelsvärm.</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7701,7 +7696,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131813681</v>
+        <v>131824196</v>
       </c>
       <c r="B65" t="n">
         <v>57904</v>
@@ -7732,7 +7727,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7741,10 +7736,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497049</v>
+        <v>497013</v>
       </c>
       <c r="R65" t="n">
-        <v>6665989</v>
+        <v>6665983</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7776,7 +7771,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7786,12 +7781,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Barkfläk, flera barkborre skadade granar. Hagelsvärm.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7818,10 +7813,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131820394</v>
+        <v>131813681</v>
       </c>
       <c r="B66" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7829,34 +7824,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kringelbackarna, Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496729</v>
+        <v>497049</v>
       </c>
       <c r="R66" t="n">
-        <v>6665578</v>
+        <v>6665989</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7898,12 +7898,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -10540,6 +10540,3495 @@
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>132006547</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>496854</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6666024</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>132019204</v>
+      </c>
+      <c r="B92" t="n">
+        <v>80373</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>496589</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6665853</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På asp med bohål</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>132006133</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>496784</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6665911</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>132009641</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57094</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>496787</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6665825</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>132002686</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>496613</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6665889</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>132006432</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>496806</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6665954</v>
+      </c>
+      <c r="S96" t="n">
+        <v>25</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>132007636</v>
+      </c>
+      <c r="B97" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>497050</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6666002</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>132009213</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>496946</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6665747</v>
+      </c>
+      <c r="S98" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>132009358</v>
+      </c>
+      <c r="B99" t="n">
+        <v>57094</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>496894</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6665788</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>132004070</v>
+      </c>
+      <c r="B100" t="n">
+        <v>80333</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>496647</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6665912</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>132001358</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>496696</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6665908</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>132002228</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>496613</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6665830</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>132006594</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>496854</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6666024</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>132006450</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57094</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>496840</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6665984</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>132001832</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>496637</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6665866</v>
+      </c>
+      <c r="S105" t="n">
+        <v>2</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>132003345</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>496632</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6666056</v>
+      </c>
+      <c r="S106" t="n">
+        <v>1</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>132009484</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>496894</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6665788</v>
+      </c>
+      <c r="S107" t="n">
+        <v>1</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>132003027</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>496547</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6665988</v>
+      </c>
+      <c r="S108" t="n">
+        <v>1</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>132006808</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91803</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>496884</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6666083</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>132005875</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>496725</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6665872</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>132005967</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57094</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>496763</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6665923</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>132002892</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79268</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>496544</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6665985</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>132003524</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>496635</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6665975</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>132019425</v>
+      </c>
+      <c r="B114" t="n">
+        <v>80246</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>392</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>496650</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6665930</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>132002027</v>
+      </c>
+      <c r="B115" t="n">
+        <v>80373</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>496637</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6665866</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>132003181</v>
+      </c>
+      <c r="B116" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>496609</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6666053</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>132007789</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>497051</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6665983</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>132008341</v>
+      </c>
+      <c r="B118" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>497125</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6665776</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>132001924</v>
+      </c>
+      <c r="B119" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>496637</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6665866</v>
+      </c>
+      <c r="S119" t="n">
+        <v>2</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>132002664</v>
+      </c>
+      <c r="B120" t="n">
+        <v>57906</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>496613</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6665889</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>132010010</v>
+      </c>
+      <c r="B121" t="n">
+        <v>80333</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>496787</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6665825</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>132009985</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>496696</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6665831</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
